--- a/data/trans_camb/P15-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P15-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,95</t>
+          <t>-2,9; 2,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 0,6</t>
+          <t>-4,9; 0,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 1,73</t>
+          <t>-4,05; 1,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,12</t>
+          <t>-0,1; 5,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,96</t>
+          <t>-0,56; 4,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,28</t>
+          <t>-0,97; 3,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,38</t>
+          <t>-0,72; 3,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,86</t>
+          <t>-2,06; 2,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,88</t>
+          <t>-1,82; 1,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 42,53</t>
+          <t>-29,02; 43,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 8,99</t>
+          <t>-50,52; 11,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 25,79</t>
+          <t>-42,98; 25,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 131,35</t>
+          <t>-2,06; 135,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 127,42</t>
+          <t>-10,29; 119,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 79,8</t>
+          <t>-15,64; 87,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 60,45</t>
+          <t>-9,3; 57,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 31,92</t>
+          <t>-27,24; 35,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 31,65</t>
+          <t>-23,19; 32,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,85</t>
+          <t>-3,41; 1,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; -0,41</t>
+          <t>-5,45; -0,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; -0,1</t>
+          <t>-6,72; -0,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,45</t>
+          <t>-1,05; 3,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,7</t>
+          <t>-3,45; 0,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,32</t>
+          <t>-2,24; 2,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,88</t>
+          <t>-1,53; 2,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,59</t>
+          <t>-3,67; -0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,12</t>
+          <t>-3,71; 0,19</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 26,18</t>
+          <t>-33,26; 24,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,23; -5,28</t>
+          <t>-54,78; -6,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,63; -2,04</t>
+          <t>-68,2; -2,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 71,46</t>
+          <t>-14,96; 73,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,36; 14,71</t>
+          <t>-48,05; 12,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 47,44</t>
+          <t>-31,78; 43,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 28,84</t>
+          <t>-18,73; 31,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,71; -8,51</t>
+          <t>-44,4; -7,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 1,74</t>
+          <t>-46,15; 2,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 3,73</t>
+          <t>-1,79; 3,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 0,4</t>
+          <t>-4,51; 0,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -0,21</t>
+          <t>-5,28; -0,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,97</t>
+          <t>-0,17; 4,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,94</t>
+          <t>-3,39; 1,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 2,09</t>
+          <t>-3,74; 2,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,3</t>
+          <t>-0,29; 3,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,22</t>
+          <t>-3,18; 0,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,14</t>
+          <t>-3,4; 0,39</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 72,48</t>
+          <t>-21,73; 73,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,69; 8,61</t>
+          <t>-52,33; 12,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,61; -3,89</t>
+          <t>-62,32; -1,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 122,84</t>
+          <t>-3,58; 122,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,71; 26,63</t>
+          <t>-52,28; 36,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,58; 49,04</t>
+          <t>-58,13; 49,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 66,24</t>
+          <t>-4,6; 69,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,95; 5,75</t>
+          <t>-47,58; 4,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,76; 1,52</t>
+          <t>-50,28; 6,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,99</t>
+          <t>1,31; 5,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,72</t>
+          <t>-1,47; 3,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,77</t>
+          <t>-1,85; 2,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,47</t>
+          <t>0,48; 4,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,64</t>
+          <t>-0,31; 3,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,73</t>
+          <t>-0,18; 3,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,49</t>
+          <t>1,31; 4,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,55</t>
+          <t>-0,37; 2,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,61</t>
+          <t>-0,19; 2,66</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,51; 121,51</t>
+          <t>18,88; 124,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 56,48</t>
+          <t>-21,94; 64,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 58,85</t>
+          <t>-27,2; 56,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,81; 125,7</t>
+          <t>7,24; 119,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 100,01</t>
+          <t>-6,64; 96,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 104,45</t>
+          <t>-3,72; 106,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,93; 99,6</t>
+          <t>22,85; 101,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 54,98</t>
+          <t>-7,35; 57,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 58,95</t>
+          <t>-3,6; 59,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,41</t>
+          <t>-0,28; 2,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,32</t>
+          <t>-2,71; -0,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,23</t>
+          <t>-3,3; -0,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,24</t>
+          <t>0,88; 3,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,36</t>
+          <t>-0,94; 1,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,92</t>
+          <t>-0,62; 1,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,4</t>
+          <t>0,65; 2,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,24</t>
+          <t>-1,39; 0,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,45</t>
+          <t>-1,6; 0,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 36,24</t>
+          <t>-3,48; 32,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,96; -5,06</t>
+          <t>-33,32; -3,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,03; -3,14</t>
+          <t>-41,11; -3,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12,14; 67,82</t>
+          <t>15,42; 67,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 29,61</t>
+          <t>-15,8; 27,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 40,77</t>
+          <t>-10,95; 36,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,49; 41,1</t>
+          <t>9,39; 41,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 4,09</t>
+          <t>-21,22; 3,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 7,79</t>
+          <t>-24,27; 7,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P15-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,05</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,93</t>
+          <t>-3,01; 2,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,75</t>
+          <t>-4,71; 0,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,75</t>
+          <t>-4,04; 2,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,52</t>
+          <t>-0,21; 5,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,77</t>
+          <t>-0,59; 4,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,4</t>
+          <t>-0,88; 3,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,34</t>
+          <t>-0,73; 3,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,07</t>
+          <t>-1,97; 2,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,86</t>
+          <t>-1,78; 1,91</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>-13,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-0,27%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 43,16</t>
+          <t>-31,54; 42,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,52; 11,86</t>
+          <t>-49,4; 8,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 25,24</t>
+          <t>-41,01; 31,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 135,1</t>
+          <t>-6,3; 116,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 119,87</t>
+          <t>-9,85; 114,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 87,44</t>
+          <t>-13,95; 90,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 57,2</t>
+          <t>-8,87; 56,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 35,06</t>
+          <t>-24,75; 35,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 32,73</t>
+          <t>-22,93; 32,57</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-0,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,8</t>
+          <t>-3,36; 1,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -0,38</t>
+          <t>-5,21; -0,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,72; -0,15</t>
+          <t>-4,2; 0,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,62</t>
+          <t>-1,04; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,6</t>
+          <t>-3,63; 0,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,07</t>
+          <t>-2,36; 1,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,01</t>
+          <t>-1,62; 1,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -0,51</t>
+          <t>-3,74; -0,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,19</t>
+          <t>-2,7; 0,88</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-35,82%</t>
+          <t>-18,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,46%</t>
+          <t>-3,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-21,98%</t>
+          <t>-12,34%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 24,06</t>
+          <t>-33,61; 25,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,78; -6,39</t>
+          <t>-51,35; -6,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,2; -2,62</t>
+          <t>-42,42; 11,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 73,8</t>
+          <t>-14,11; 68,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,05; 12,9</t>
+          <t>-48,97; 12,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 43,4</t>
+          <t>-33,16; 42,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 31,2</t>
+          <t>-20,01; 28,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,4; -7,12</t>
+          <t>-44,24; -8,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 2,61</t>
+          <t>-31,56; 13,63</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-0,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,93</t>
+          <t>-2,02; 3,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,62</t>
+          <t>-4,35; 0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,22</t>
+          <t>-5,14; -0,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,75</t>
+          <t>-0,27; 4,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,24</t>
+          <t>-3,2; 0,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,21</t>
+          <t>-1,11; 3,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,5</t>
+          <t>-0,17; 3,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,26</t>
+          <t>-3,22; 0,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,39</t>
+          <t>-2,76; 0,66</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-38,44%</t>
+          <t>-39,08%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-7,48%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-24,37%</t>
+          <t>-13,78%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 73,1</t>
+          <t>-24,65; 70,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,33; 12,49</t>
+          <t>-53,63; 11,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,32; -1,13</t>
+          <t>-62,62; -2,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 122,19</t>
+          <t>-5,94; 117,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 36,22</t>
+          <t>-52,86; 27,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,13; 49,07</t>
+          <t>-19,64; 84,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 69,7</t>
+          <t>-3,3; 71,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 4,64</t>
+          <t>-45,93; 3,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 6,02</t>
+          <t>-38,48; 14,69</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,94</t>
+          <t>1,15; 6,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,04</t>
+          <t>-1,64; 2,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,66</t>
+          <t>-1,95; 2,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,39</t>
+          <t>0,49; 4,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,57</t>
+          <t>-0,42; 3,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,76</t>
+          <t>0,28; 3,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,55</t>
+          <t>1,49; 4,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,59</t>
+          <t>-0,41; 2,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,66</t>
+          <t>-0,14; 2,62</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,88; 124,75</t>
+          <t>17,16; 128,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 64,88</t>
+          <t>-23,29; 61,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 56,16</t>
+          <t>-28,88; 55,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,24; 119,15</t>
+          <t>8,83; 131,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 96,03</t>
+          <t>-8,81; 100,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 106,6</t>
+          <t>4,94; 111,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,85; 101,65</t>
+          <t>25,89; 103,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 57,18</t>
+          <t>-7,84; 59,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 59,19</t>
+          <t>-2,59; 58,97</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,22</t>
+          <t>-0,29; 2,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -0,29</t>
+          <t>-2,8; -0,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,26</t>
+          <t>-2,33; 0,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,18</t>
+          <t>0,87; 3,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,28</t>
+          <t>-0,88; 1,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,71</t>
+          <t>-0,07; 1,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,44</t>
+          <t>0,58; 2,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,19</t>
+          <t>-1,45; 0,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,45</t>
+          <t>-0,74; 0,89</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-22,05%</t>
+          <t>-15,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-7,62%</t>
+          <t>-0,82%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 32,82</t>
+          <t>-3,56; 36,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,32; -3,96</t>
+          <t>-34,67; -4,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,11; -3,8</t>
+          <t>-29,32; 3,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15,42; 67,5</t>
+          <t>14,68; 68,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 27,4</t>
+          <t>-15,39; 27,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 36,65</t>
+          <t>-1,29; 42,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,39; 41,84</t>
+          <t>8,68; 41,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 3,2</t>
+          <t>-21,5; 4,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 7,37</t>
+          <t>-11,23; 14,87</t>
         </is>
       </c>
     </row>
